--- a/Result/profitability/3147.xlsx
+++ b/Result/profitability/3147.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM57"/>
+  <dimension ref="A1:AM58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.63</v>
       </c>
       <c r="M2" t="n">
-        <v>2.655</v>
+        <v>3.41625</v>
       </c>
       <c r="N2" t="n">
-        <v>13.46</v>
+        <v>13.2925</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.39</v>
       </c>
       <c r="M3" t="n">
-        <v>2.515</v>
+        <v>2.6425</v>
       </c>
       <c r="N3" t="n">
-        <v>13.5175</v>
+        <v>13.0975</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.18</v>
       </c>
       <c r="M4" t="n">
-        <v>1.715</v>
+        <v>2.2225</v>
       </c>
       <c r="N4" t="n">
-        <v>13.57375</v>
+        <v>13.815</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>1.28</v>
       </c>
       <c r="M5" t="n">
-        <v>1.4325</v>
+        <v>2.32125</v>
       </c>
       <c r="N5" t="n">
-        <v>13.77375</v>
+        <v>13.24875</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,16 +1137,16 @@
         <v>1.46</v>
       </c>
       <c r="M6" t="n">
-        <v>1.55375</v>
+        <v>2.21375</v>
       </c>
       <c r="N6" t="n">
-        <v>13.27</v>
+        <v>12.95375</v>
       </c>
       <c r="O6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.85</v>
       </c>
       <c r="M7" t="n">
-        <v>1.37</v>
+        <v>2.00625</v>
       </c>
       <c r="N7" t="n">
-        <v>13.015</v>
+        <v>12.73625</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -7667,6 +7667,133 @@
       </c>
       <c r="AM57" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>3147</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>5869</v>
+      </c>
+      <c r="D58" t="n">
+        <v>5185</v>
+      </c>
+      <c r="E58" t="n">
+        <v>683</v>
+      </c>
+      <c r="F58" t="n">
+        <v>11.64</v>
+      </c>
+      <c r="G58" t="n">
+        <v>429</v>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>7.32%</t>
+        </is>
+      </c>
+      <c r="I58" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J58" t="n">
+        <v>428</v>
+      </c>
+      <c r="K58" t="n">
+        <v>332</v>
+      </c>
+      <c r="L58" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="M58" t="n">
+        <v>3.52625</v>
+      </c>
+      <c r="N58" t="n">
+        <v>13.22375</v>
+      </c>
+      <c r="O58" t="n">
+        <v>1</v>
+      </c>
+      <c r="P58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>1</v>
+      </c>
+      <c r="R58" t="n">
+        <v>0</v>
+      </c>
+      <c r="S58" t="n">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>0</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
+      </c>
+      <c r="V58" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W58" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="X58" t="n">
+        <v>1.076502732240437</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>-0.9399999999999995</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>-0.07472178060413348</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>7.109999999999999</v>
+      </c>
+      <c r="AB58" t="n">
+        <v>14.51020408163265</v>
+      </c>
+      <c r="AC58" t="n">
+        <v>-4.199999999999999</v>
+      </c>
+      <c r="AD58" t="n">
+        <v>-0.2651515151515151</v>
+      </c>
+      <c r="AE58" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF58" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK58" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL58" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM58" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
